--- a/Assessment Questions/CDE/DATA ENGINEERING ASSOCIATE/DATA ORCHESTRATION WITH APACHE AIRFLOW/Data Orchestration Overview/data_orchestration_questions.xlsx
+++ b/Assessment Questions/CDE/DATA ENGINEERING ASSOCIATE/DATA ORCHESTRATION WITH APACHE AIRFLOW/Data Orchestration Overview/data_orchestration_questions.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Orchestration" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="questions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -434,12 +434,12 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Correct Answer</t>
+          <t>Explanation</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Explanation</t>
+          <t>Question Type</t>
         </is>
       </c>
     </row>
@@ -461,12 +461,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>Data orchestration involves managing and coordinating data pipelines across different systems.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data orchestration involves managing and coordinating data pipelines across different systems.</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
@@ -488,12 +488,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Apache Airflow is one of the most popular data orchestration tools.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Apache Airflow is one of the most popular data orchestration tools.</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
@@ -508,15 +508,14 @@
           <t>One-word</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Automation</t>
+          <t>The primary goal is to automate and manage data workflows efficiently.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>The primary goal is to automate and manage data workflows efficiently.</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -538,12 +537,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Data orchestration helps manage complex dependencies across multiple sources.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data orchestration helps manage complex dependencies across multiple sources.</t>
+          <t>Scenario-Based</t>
         </is>
       </c>
     </row>
@@ -558,15 +557,14 @@
           <t>One-word</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Directed Acyclic Graph</t>
+          <t>DAG represents the workflow structure with directional dependencies.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>DAG represents the workflow structure with directional dependencies.</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -588,12 +586,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>Data orchestration reduces manual intervention through automation.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data orchestration reduces manual intervention through automation.</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
@@ -608,15 +606,14 @@
           <t>One-word</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Centralized</t>
+          <t>Orchestration uses a central controller while choreography is decentralized.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Orchestration uses a central controller while choreography is decentralized.</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -638,12 +635,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>Orchestration tools provide retry mechanisms and error handling.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Orchestration tools provide retry mechanisms and error handling.</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
@@ -658,15 +655,14 @@
           <t>One-word</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Repeatable</t>
+          <t>Idempotent tasks produce the same result regardless of how many times they run.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Idempotent tasks produce the same result regardless of how many times they run.</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -688,12 +684,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Dependency management ensures tasks wait for prerequisites.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Dependency management ensures tasks wait for prerequisites.</t>
+          <t>Scenario-Based</t>
         </is>
       </c>
     </row>
@@ -708,15 +704,14 @@
           <t>One-word</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Orchestration</t>
+          <t>It sits between data ingestion and storage/processing layers.</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>It sits between data ingestion and storage/processing layers.</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -738,12 +733,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Cron jobs cannot handle complex dependencies between tasks.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Cron jobs cannot handle complex dependencies between tasks.</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
@@ -758,15 +753,14 @@
           <t>One-word</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Service Level Agreement</t>
+          <t>SLA defines expected completion times for workflows.</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>SLA defines expected completion times for workflows.</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -788,12 +782,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Managing complex dependencies is a key challenge.</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Managing complex dependencies is a key challenge.</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
@@ -808,15 +802,14 @@
           <t>One-word</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Monitoring</t>
+          <t>Observability means being able to monitor and understand workflow execution.</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Observability means being able to monitor and understand workflow execution.</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -838,12 +831,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Logging provides audit trails for compliance.</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Logging provides audit trails for compliance.</t>
+          <t>Scenario-Based</t>
         </is>
       </c>
     </row>
@@ -858,15 +851,14 @@
           <t>One-word</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Reliability</t>
+          <t>It ensures tasks can be retried without causing data issues.</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>It ensures tasks can be retried without causing data issues.</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -881,15 +873,14 @@
           <t>One-word</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Tech/FAANG</t>
+          <t>Companies like Facebook and Airbnb developed early orchestration tools.</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Companies like Facebook and Airbnb developed early orchestration tools.</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -904,15 +895,14 @@
           <t>One-word</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Scope</t>
+          <t>Workflow is broader; pipeline focuses on data movement.</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Workflow is broader; pipeline focuses on data movement.</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -934,12 +924,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Orchestration platforms handle large-scale dependencies effectively.</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Orchestration platforms handle large-scale dependencies effectively.</t>
+          <t>Scenario-Based</t>
         </is>
       </c>
     </row>
